--- a/역설계_심화_제형별.xlsx
+++ b/역설계_심화_제형별.xlsx
@@ -7,21 +7,22 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="크림" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="로션" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="밤" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="세럼" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="세정" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="토너·미스트" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="젤" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="팩·마스크·패드" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="페이스·바디오일" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="색조" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="헤어세정" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="입욕·스크럽" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="완제베이스+활성" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="생활화학" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="공통교훈" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="★히어로" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="크림" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="로션" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="밤" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="세럼" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="세정" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="토너·미스트" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="젤" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="팩·마스크·패드" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="페이스·바디오일" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="색조" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="헤어세정" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="입욕·스크럽" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="완제베이스+활성" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="생활화학" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="공통교훈" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,7 +513,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[크림]  석류영양크림 — 역설계 심화</t>
+          <t>[★히어로]  시크 진정 밸런스 크림 (sebum-calm-cream v2) — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -531,7 +532,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>라벤더워터 베이스에 PUFA 풍부 오일(로즈힙·햄프)로 영양막을 얹고, 석류·코엔자임Q10로 탄력을 노린 리치 영양 크림.</t>
+          <t>예민·지성(지루 경향) 피부용 무향 진정 크림. 말라세지아가 못 먹는 에몰리언트만 써서 '유분은 주되 효모는 안 키우는' 설계. 제약이 곧 차별화인 전문 처방.</t>
         </is>
       </c>
     </row>
@@ -543,73 +544,75 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>수상 53(라벤더워터) · 유상 31(로즈힙 19 + 햄프씨드 11 + 세틸알코올 1) · 유화 3(올리브유화왁스) · 활성 11(석류 4 + Q10 3 + 히알루론 3) · 방부 2 · 향 &lt;1</t>
+          <t>수상 77(물 63.5 + 폴리올·수용성 활성) · 유상 17(몬타노브68 4 + 세틸 2 + 스쿠알란 5 + MCT 3 + 디메치콘 3) · 냉각 활성/방부 6(병풀·판테놀·녹차 2 + 페녹시 0.7 + 헥산디올 1)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="90" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① 유화 설계 — 왜 올리브유화왁스 3% + 세틸알코올 1%?</t>
+          <t>① 왜 몬타노브68 4% — 말라세지아-세이프의 핵심</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· 올리브유화왁스(Cetearyl/Sorbitan Olivate)는 O/W 유화제이면서 지방알코올을 함유해 점도·바디감까지 준다(특징에 '유화제 겸 경화제'). 글루코사이드/올리베이트계라 저자극·액정 구조로 보습감이 좋다.
-· 유상 31%에 유화제는 3%뿐 → 유화제:유상 ≈ 0.1로 빠듯. 세틸알코올 1%가 공유화·증점(consistency factor)으로 유화막을 보강하고 크림을 탄탄하게. 세틸알코올은 유화제가 아니라 '보조'인 점이 핵심.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
+          <t>· 몬타노브68(Cetearyl Alcohol &amp; Cetearyl Glucoside) = 글루코사이드계 O/W 유화제, 액정 구조로 저자극. 핵심은 '말라세지아가 먹지 않는' 유화제 — 올리브계(올리베이트)·GMS SE는 지방산/에스터라 회색지대 → 회피.
+· 유상 17%에 유화제 4%(비 ≈ 0.24) + 세틸알코올 2%가 공유화·바디 보강. (조달: glyceryl-stearate-citrate 국내 난조 → 몬타노브68 동일 4%로 교체, HLB 재검증 완료.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="105" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② 활성 조합의 의도</t>
+          <t>② 유상 설계 — '지방산 오일 전면 배제'가 컨셉</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 석류추출물 + 코엔자임Q10: 항산화·탄력 각도. Q10은 나이 들며 감소하는 세포 에너지 보조 → '탄력·노화 결' 컨셉.
-· 히알루론산 3%: 수분 저장. 유분 31%로 무거울 수 있는 처방에 수분-유분 균형.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
+          <t>· 말라세지아(효모)는 C11~24 지방산을 먹이로 대사 → 올리브·코코넛·호호바·버터류 전면 배제. 대신:
+   - 스쿠알란 5%(C30 탄화수소, 먹이 아님, 초경량)
+   - MCT 3%(C8/C10 중쇄, 먹이 아님)
+   - 디메치콘 3%(실리콘, 비유성 매끈·막)
+· '유분감·보습막은 주되 효모 먹이는 안 준다' → 기능 제약을 원료 선택으로 푼 설계. 이게 제품의 전문 앵글.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="75" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>③ 핵심 비율 결정</t>
+          <t>③ 수상·보습 — 지성용 '무유분 보습'</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 수상 53% + 유상 31% → 유분비 높은 전형적 '영양 크림'(로션이면 유상 10~15%). 건성·노화 타깃.
-· 유화 3%는 최소선 → 세틸알코올 없으면 분리 위험. '유화제 빠듯할 땐 지방알코올로 보완'의 교과서.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+          <t>· 유분을 못 늘리니 수분으로 채운다: 다중 히알루론산 1%(고·중·저분자 층별), 글리세린 5%, 펜틸렌글라이콜 3%(폴리올=보습+방부보조, 세이프).
+· 활성: 나이아신아마이드 2%(피지·장벽·톤) + 아연PCA 1%(피지조절) + 베타글루칸·알란토인(진정) + 병풀·판테놀(장벽·진정) + 녹차 2%(EGCG 피지·항산화) → '피지·진정·장벽' 삼각, 전부 수용성(무향·세이프 유지).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>④ 바꾸면?(what-if)</t>
+          <t>④ 공정 설계 — 왜 3상(A/B/C)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 로즈힙·햄프는 고불포화(PUFA) 오일 → 산패 빠름. 그런데 보존제는 항균(천연한방)뿐, 산화방지제가 없다 → 비타민E(토코페롤) 0.2~0.5% 추가하면 보존기간 급증. (이 레시피 최대 개선점)
-· 지성·여드름 타깃이면 로즈힙·햄프 대신 스쿠알란·MCT(가볍고 산패 안정), 유상 15~20%로 → 가벼운 크림.
-· 유화제를 몬타노브68로 바꾸면 더 매끈한 액정 질감(히어로 방향).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>· A(수상)·B(유상)를 70~75℃ 유화 → 열 안정 성분만. 열에 약한 병풀·판테놀·녹차·방부(페녹시)는 40℃ 이하 C상에서 투입 → 활성 파괴·휘발 방지(전문적).
+· 잔탄검 0.3%는 글리세린에 선분산(덩어리 방지).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>⑤ 배우는 점</t>
+          <t>⑤ 배우는 점 / 점검·개선 포인트</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· 유화제:유상 비가 낮으면 지방알코올(세틸/세테아릴)로 바디·안정 보강.
-· PUFA 오일엔 반드시 항산화(Vit E) — 항균 보존제와 산화방지제는 다른 일.</t>
+          <t>· 제약이 컨셉을 만든다 — '말라세지아-세이프'가 팔레트를 좁히고 그게 곧 차별화.
+· 점검: ⓐ 몬타노브68 HLB·유상 조합 안정(파일럿 유화 확인) ⓑ pH 5.0~5.5 조정(나이아신·녹차·방부 모두 산성 선호) ⓒ 다중 HA 수화 덩어리 ⓓ 페녹시 0.7%+헥산디올 1% 방부는 챌린지 테스트로 실증 필수 ⓔ 화장품이라 '치료·완화' 표방 금지.</t>
         </is>
       </c>
     </row>
@@ -638,7 +641,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[색조]  체리립밤 — 역설계 심화</t>
+          <t>[페이스·바디오일]  아르간페이셜오일 — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -657,11 +660,11 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>자초를 우려낸 오일로 '천연 색'을 내고 왁스로 굳힌 틴티드 립밤.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>아르간+로즈힙 2종 블렌드의 무수 페이셜오일. 오일을 '지방산 프로파일'로 고른 사례.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>골격(%)</t>
@@ -669,43 +672,43 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>유상/활성 86(자초인퓨즈오일 46 + 시어버터 17 + 로즈힙 17 + 토코페롤 6) · 경화 14(칸데릴라왁스) · 향 &lt;1(체리플레이버)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>유상 100(아르간 60 + 로즈힙 40) · 향 &lt;1(네롤리 EO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① 천연 색소 = 인퓨즈</t>
+          <t>① 왜 이 2종 오일</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· 자초(지치 뿌리)를 호호바오일에 우려내면 붉은/보라 색소가 오일로 추출됨 → 합성 색소 없이 틴트. '색을 원료로 사는 게 아니라 우려서 만든다'.</t>
+          <t>· 아르간(올레인·리놀레산 균형, 토코페롤·폴리페놀 풍부 → 비교적 안정)과 로즈힙(고 리놀레/리놀렌산=PUFA, 재생·노화 각도지만 산패 빠름)의 조합. 아르간의 토코페롤이 로즈힙 산패를 일부 늦춘다 → '안정 오일 + 기능 오일' 페어링.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② 왁스로 굳기</t>
+          <t>② 무수 설계</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 칸데릴라왁스 14% → 밀어 바르는 립밤 경도(밤과 같은 원리, 립이라 식용 플레이버). 칸데릴라는 식물성·단단.</t>
+          <t>· 물 없음 → 방부 불필요, 물 유입 금지. 산패가 유일한 적 → 차광·밀폐, 토코페롤 추가 여지.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>③ 산패 대비 (크림과 대조)</t>
+          <t>③ 핵심 비율</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 로즈힙(PUFA)이 들어가는데 여기선 토코페롤 6%를 넣었다 → 석류크림이 빠뜨린 걸 이 처방은 챙김. 좋은 비교 학습.</t>
+          <t>· 60:40은 '기능(로즈힙)을 충분히 주되 아르간으로 안정·발림 확보'. EO는 2방울(&lt;1%)로 향만.</t>
         </is>
       </c>
     </row>
@@ -717,13 +720,13 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 색 진하게 → 자초 인퓨즈를 더 진하게/오래 우림.
-· 더 단단(여름·스틱) → 칸데릴라 18~22%.
-· 틴트 지속 → 소량 색소 파우더(마이카) 분산 추가.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>· 지성·여드름이면 로즈힙 줄이고 스쿠알란·호호바(말라세지아 세이프·가벼움)로.
+· 미스트 위 덧바르는 3초 보습용엔 이대로 좋음.
+· 토코페롤 0.3% 추가로 보존 강화.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>⑤ 배우는 점</t>
@@ -731,8 +734,8 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· 천연 색조는 '인퓨즈'로 얻을 수 있다.
-· 립 = 식용 플레이버·안전 색소. PUFA엔 토코페롤(이 처방이 모범).</t>
+          <t>· 오일은 '지방산 프로파일'로 고른다(올레인=안정·유연, 리놀레=가벼움·장벽, PUFA=기능이나 산패↑).
+· 블렌딩으로 안정×기능 균형. EO는 반드시 캐리어에 희석.</t>
         </is>
       </c>
     </row>
@@ -761,7 +764,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[헤어세정]  허브두피샴푸 — 역설계 심화</t>
+          <t>[색조]  체리립밤 — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -780,7 +783,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>완성 물비누베이스에 두피 활성·EO만 더한 '베이스 커스터마이즈'형 샴푸.</t>
+          <t>자초를 우려낸 오일로 '천연 색'을 내고 왁스로 굳힌 틴티드 립밤.</t>
         </is>
       </c>
     </row>
@@ -792,47 +795,47 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>계면 81(고급물비누베이스) · 활성 17(에스피노질리아·네틀·EM·판테놀) · 향 2(로즈마리·레몬글라스) · 유상 &lt;1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>유상/활성 86(자초인퓨즈오일 46 + 시어버터 17 + 로즈힙 17 + 토코페롤 6) · 경화 14(칸데릴라왁스) · 향 &lt;1(체리플레이버)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① 완제 베이스 + 소량 활성</t>
+          <t>① 천연 색소 = 인퓨즈</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· 세정·거품의 몸통은 이미 완성된 '물비누베이스' 81%. 여기에 두피 활성(네틀=피지, 에스피노질리아=강화, EM=비듬)과 EO만 소량 더함 → 처방이 쉽고 실패 적음(완제베이스 전략).</t>
+          <t>· 자초(지치 뿌리)를 호호바오일에 우려내면 붉은/보라 색소가 오일로 추출됨 → 합성 색소 없이 틴트. '색을 원료로 사는 게 아니라 우려서 만든다'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② 왜 이 활성들</t>
+          <t>② 왁스로 굳기</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 두피 트러블·피지·비듬 각도. 판테놀은 보습 보강.</t>
+          <t>· 칸데릴라왁스 14% → 밀어 바르는 립밤 경도(밤과 같은 원리, 립이라 식용 플레이버). 칸데릴라는 식물성·단단.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>③ 핵심 비율</t>
+          <t>③ 산패 대비 (크림과 대조)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 활성 합 17%는 베이스가 허용하는 한도 내. 너무 많이 넣으면 베이스의 점도·거품·보존이 깨진다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+          <t>· 로즈힙(PUFA)이 들어가는데 여기선 토코페롤 6%를 넣었다 → 석류크림이 빠뜨린 걸 이 처방은 챙김. 좋은 비교 학습.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>④ 바꾸면?(what-if)</t>
@@ -840,9 +843,9 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 세정 후 알칼리로 뜬 모발 → '로즈마리 구연산린스'(산성 린스)로 pH 되돌리면 찰랑(샴푸-린스 한 쌍).
-· 더 순하게 → 베이스 희석↑.
-· 탈모 각도면 로즈마리·페퍼민트 EO.</t>
+          <t>· 색 진하게 → 자초 인퓨즈를 더 진하게/오래 우림.
+· 더 단단(여름·스틱) → 칸데릴라 18~22%.
+· 틴트 지속 → 소량 색소 파우더(마이카) 분산 추가.</t>
         </is>
       </c>
     </row>
@@ -854,8 +857,8 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· 완제 베이스는 '활성 소량 추가'가 정석(과투입 금지).
-· 샴푸(알칼리) 뒤 산성 린스로 pH 복원 = 모발 정돈 원리.</t>
+          <t>· 천연 색조는 '인퓨즈'로 얻을 수 있다.
+· 립 = 식용 플레이버·안전 색소. PUFA엔 토코페롤(이 처방이 모범).</t>
         </is>
       </c>
     </row>
@@ -884,7 +887,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[입욕·스크럽]  일랑일랑 버블바스붐 — 역설계 심화</t>
+          <t>[헤어세정]  허브두피샴푸 — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -903,11 +906,11 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>베이킹소다+구연산의 발포 반응으로 물에서 보글거리는 바스붐.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+          <t>완성 물비누베이스에 두피 활성·EO만 더한 '베이스 커스터마이즈'형 샴푸.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>골격(%)</t>
@@ -915,31 +918,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>점증/pH 79(소다 43 + 구연산 21 + 옥수수전분 14) · 소금 21(사해소금)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>계면 81(고급물비누베이스) · 활성 17(에스피노질리아·네틀·EM·판테놀) · 향 2(로즈마리·레몬글라스) · 유상 &lt;1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① 발포의 원리</t>
+          <t>① 완제 베이스 + 소량 활성</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· 베이킹소다(염기) + 구연산(산)이 물에 닿으면 반응해 CO2(거품) 발생. 핵심은 '건조 상태로 보관' — 습기에 미리 반응하면 다 터져 못 쓴다 → 건조·밀봉.</t>
+          <t>· 세정·거품의 몸통은 이미 완성된 '물비누베이스' 81%. 여기에 두피 활성(네틀=피지, 에스피노질리아=강화, EM=비듬)과 EO만 소량 더함 → 처방이 쉽고 실패 적음(완제베이스 전략).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② 전분·소금의 역할</t>
+          <t>② 왜 이 활성들</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 옥수수전분 = 반응 속도 완충·뭉침 방지·연마. 사해소금 = 미네랄·삼투압 노폐물. 소금 과다는 성형·발포 방해.</t>
+          <t>· 두피 트러블·피지·비듬 각도. 판테놀은 보습 보강.</t>
         </is>
       </c>
     </row>
@@ -951,11 +954,11 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 소다:구연산 ≈ 2:1(소다를 더)이 일반적. 몰드 성형 시 수분은 '분무'로 아주 조금만(많으면 미리 반응).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
+          <t>· 활성 합 17%는 베이스가 허용하는 한도 내. 너무 많이 넣으면 베이스의 점도·거품·보존이 깨진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>④ 바꾸면?(what-if)</t>
@@ -963,9 +966,9 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 더 촉촉 → 유화제+오일 소량(욕조 미끄럼 주의).
-· 색·향 → 소량 색소·EO(소다에 미리 비벼 흡수).
-· 거품↑ → SLSA 등 순한 기포제.</t>
+          <t>· 세정 후 알칼리로 뜬 모발 → '로즈마리 구연산린스'(산성 린스)로 pH 되돌리면 찰랑(샴푸-린스 한 쌍).
+· 더 순하게 → 베이스 희석↑.
+· 탈모 각도면 로즈마리·페퍼민트 EO.</t>
         </is>
       </c>
     </row>
@@ -977,8 +980,8 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· 산-염기 발포 = 물 금지·건조 보관. 성형 수분은 분무로 최소.
-· 기능은 전분/소금/기포제 비율로 조절.</t>
+          <t>· 완제 베이스는 '활성 소량 추가'가 정석(과투입 금지).
+· 샴푸(알칼리) 뒤 산성 린스로 pH 복원 = 모발 정돈 원리.</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1010,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[완제베이스+활성]  EFGF 리뉴 수분크림 — 역설계 심화</t>
+          <t>[입욕·스크럽]  일랑일랑 버블바스붐 — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -1026,11 +1029,11 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>알로에겔 베이스에 EGF·FGF 등 고가 활성을 ppm 단위로 올린 '활성 집약' 겔크림.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>베이킹소다+구연산의 발포 반응으로 물에서 보글거리는 바스붐.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>골격(%)</t>
@@ -1038,31 +1041,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>활성 95(알로에겔 83 + EGF 5 + FGF 5 + 나이아신 3 + 리피듀어 3) · 방부 1 · 유상 &lt;1(씨벅턴)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>점증/pH 79(소다 43 + 구연산 21 + 옥수수전분 14) · 소금 21(사해소금)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① ppm 성분 다루기</t>
+          <t>① 발포의 원리</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· EGF/FGF는 '1ppm 또는 10ppm 택'처럼 극미량으로 쓰는 재생 신호 활성(식약처 기준). 원료 투입%(5%)와 실제 활성 농도(ppm)는 다르다 → 원료는 이미 희석된 상태. 과투입 ≠ 효과.</t>
+          <t>· 베이킹소다(염기) + 구연산(산)이 물에 닿으면 반응해 CO2(거품) 발생. 핵심은 '건조 상태로 보관' — 습기에 미리 반응하면 다 터져 못 쓴다 → 건조·밀봉.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② 베이스 = 알로에겔</t>
+          <t>② 전분·소금의 역할</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 유화 없이 알로에겔 83%가 점도+진정+수분 베이스. 활성을 '올리는' 캔버스.</t>
+          <t>· 옥수수전분 = 반응 속도 완충·뭉침 방지·연마. 사해소금 = 미네랄·삼투압 노폐물. 소금 과다는 성형·발포 방해.</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1077,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 활성 합이 95%로 보여도 대부분 알로에겔(베이스). 실제 기능 활성은 EGF/FGF/나이아신/리피듀어 소량. 나이아신 3%는 고시 미백 유효구간.</t>
+          <t>· 소다:구연산 ≈ 2:1(소다를 더)이 일반적. 몰드 성형 시 수분은 '분무'로 아주 조금만(많으면 미리 반응).</t>
         </is>
       </c>
     </row>
@@ -1086,9 +1089,9 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 유분이 거의 없어 건성엔 가벼움 → 스쿠알란·세라마이드 소량 + 유화제로 크림화.
-· 열·pH에 약한 활성(EGF/FGF)은 마지막 저온 투입.
-· 지용성 씨벅턴(오일)은 소량·가용화 고려.</t>
+          <t>· 더 촉촉 → 유화제+오일 소량(욕조 미끄럼 주의).
+· 색·향 → 소량 색소·EO(소다에 미리 비벼 흡수).
+· 거품↑ → SLSA 등 순한 기포제.</t>
         </is>
       </c>
     </row>
@@ -1100,8 +1103,8 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· 완제·ppm 활성은 '소량·저온·베이스 위'가 원칙. 원료% ≠ 활성 농도.
-· 비싼 활성일수록 안정(열·pH) 관리가 효과를 좌우.</t>
+          <t>· 산-염기 발포 = 물 금지·건조 보관. 성형 수분은 분무로 최소.
+· 기능은 전분/소금/기포제 비율로 조절.</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1133,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[생활화학]  아로마 물파스 — 역설계 심화</t>
+          <t>[완제베이스+활성]  EFGF 리뉴 수분크림 — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1152,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>위치헤이즐+에탄올 베이스에 멘톨 쿨링과 EO를 가용화해 담은 쿨링 물파스.</t>
+          <t>알로에겔 베이스에 EGF·FGF 등 고가 활성을 ppm 단위로 올린 '활성 집약' 겔크림.</t>
         </is>
       </c>
     </row>
@@ -1161,31 +1164,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>수상 ~67(위치헤이즐 48 + 에탄올 15 + 멘톨 4) · 활성 19(알로에겔) · 기타 10(인플라신) · 유화 2(올리브리퀴드) · 점증 1(하이셀) · 향 1(EO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>활성 95(알로에겔 83 + EGF 5 + FGF 5 + 나이아신 3 + 리피듀어 3) · 방부 1 · 유상 &lt;1(씨벅턴)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① 에탄올 + 가용화로 EO를 담다</t>
+          <t>① ppm 성분 다루기</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· 멘톨·EO(지용성)를 에탄올·올리브리퀴드로 녹여 수상에 분산 → 맑고 시원한 물파스. 에탄올은 소독·휘발·청량 + 가용화 보조.</t>
+          <t>· EGF/FGF는 '1ppm 또는 10ppm 택'처럼 극미량으로 쓰는 재생 신호 활성(식약처 기준). 원료 투입%(5%)와 실제 활성 농도(ppm)는 다르다 → 원료는 이미 희석된 상태. 과투입 ≠ 효과.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② 쿨링 설계</t>
+          <t>② 베이스 = 알로에겔</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 멘톨 4%가 냉감(TRPM8 자극)으로 '파스'의 시원함. EO(라벤더·티트리·로즈마리)로 진정·항균·순환.</t>
+          <t>· 유화 없이 알로에겔 83%가 점도+진정+수분 베이스. 활성을 '올리는' 캔버스.</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1200,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 하이셀 1%로 살짝 점도(흐름 제어). 알로에겔로 진정·수분. 멘톨 과다는 자극.</t>
+          <t>· 활성 합이 95%로 보여도 대부분 알로에겔(베이스). 실제 기능 활성은 EGF/FGF/나이아신/리피듀어 소량. 나이아신 3%는 고시 미백 유효구간.</t>
         </is>
       </c>
     </row>
@@ -1209,9 +1212,9 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 더 시원 → 멘톨↑(단, 자극 한계).
-· 향/EO 늘리면 가용화제(올리브리퀴드) 비례 증량.
-· 외용·생활 제형은 표방·규제 레짐(화장품 vs 의약외품)이 다름 — 반드시 확인.</t>
+          <t>· 유분이 거의 없어 건성엔 가벼움 → 스쿠알란·세라마이드 소량 + 유화제로 크림화.
+· 열·pH에 약한 활성(EGF/FGF)은 마지막 저온 투입.
+· 지용성 씨벅턴(오일)은 소량·가용화 고려.</t>
         </is>
       </c>
     </row>
@@ -1223,8 +1226,8 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· 지용성(멘톨·EO)을 수상에 → 에탄올 + 가용화제.
-· 생활·외용 제형은 규제 레짐이 화장품과 다르다.</t>
+          <t>· 완제·ppm 활성은 '소량·저온·베이스 위'가 원칙. 원료% ≠ 활성 농도.
+· 비싼 활성일수록 안정(열·pH) 관리가 효과를 좌우.</t>
         </is>
       </c>
     </row>
@@ -1238,6 +1241,129 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="108" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>[생활화학]  아로마 물파스 — 역설계 심화</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>⚠ 업계 통용 배합지식 기반 해석·학습용(예시). 효능·안전성·방부력·고시 농도는 집행 전 식약처·공급사 TDS·챌린지테스트로 검증. % 는 레시피 그램 환산 근사치.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>한 줄 요약</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>위치헤이즐+에탄올 베이스에 멘톨 쿨링과 EO를 가용화해 담은 쿨링 물파스.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>골격(%)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>수상 ~67(위치헤이즐 48 + 에탄올 15 + 멘톨 4) · 활성 19(알로에겔) · 기타 10(인플라신) · 유화 2(올리브리퀴드) · 점증 1(하이셀) · 향 1(EO)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>① 에탄올 + 가용화로 EO를 담다</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>· 멘톨·EO(지용성)를 에탄올·올리브리퀴드로 녹여 수상에 분산 → 맑고 시원한 물파스. 에탄올은 소독·휘발·청량 + 가용화 보조.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>② 쿨링 설계</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>· 멘톨 4%가 냉감(TRPM8 자극)으로 '파스'의 시원함. EO(라벤더·티트리·로즈마리)로 진정·항균·순환.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>③ 핵심 비율</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>· 하이셀 1%로 살짝 점도(흐름 제어). 알로에겔로 진정·수분. 멘톨 과다는 자극.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>④ 바꾸면?(what-if)</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>· 더 시원 → 멘톨↑(단, 자극 한계).
+· 향/EO 늘리면 가용화제(올리브리퀴드) 비례 증량.
+· 외용·생활 제형은 표방·규제 레짐(화장품 vs 의약외품)이 다름 — 반드시 확인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>⑤ 배우는 점</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>· 지용성(멘톨·EO)을 수상에 → 에탄올 + 가용화제.
+· 생활·외용 제형은 규제 레짐이 화장품과 다르다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1312,7 +1438,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[로션]  페이셜&amp;바디 라벤더 로션 — 역설계 심화</t>
+          <t>[크림]  석류영양크림 — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1457,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>라벤더워터 + 알로에겔로 산뜻한 수상을 깔고, 가벼운 오일 소량으로 얇은 보습막을 입힌 데일리 로션.</t>
+          <t>라벤더워터 베이스에 PUFA 풍부 오일(로즈힙·햄프)로 영양막을 얹고, 석류·코엔자임Q10로 탄력을 노린 리치 영양 크림.</t>
         </is>
       </c>
     </row>
@@ -1343,36 +1469,37 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>수상 52(라벤더워터) · 활성 28(알로에베라겔 22 + 세라마이드 4 + 캐모마일 2) · 유상 12(동백 8 + 녹차씨 4) · 보습 4(글리세린) · 유화 2(올리브유화왁스) · 방부 1 · 향 &lt;1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>수상 53(라벤더워터) · 유상 31(로즈힙 19 + 햄프씨드 11 + 세틸알코올 1) · 유화 3(올리브유화왁스) · 활성 11(석류 4 + Q10 3 + 히알루론 3) · 방부 2 · 향 &lt;1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="90" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① 유화 설계 — 왜 유화 2%뿐인데 되나</t>
+          <t>① 유화 설계 — 왜 올리브유화왁스 3% + 세틸알코올 1%?</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· 유상이 12%로 낮아 유화제도 2%면 충분(유화제:유상 ≈ 0.17 → 가벼운 로션 구간). 크림과 비교하면 유분·유화제 모두 절반 이하 → 같은 유화제라도 비율로 로션↔크림이 갈린다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
+          <t>· 올리브유화왁스(Cetearyl/Sorbitan Olivate)는 O/W 유화제이면서 지방알코올을 함유해 점도·바디감까지 준다(특징에 '유화제 겸 경화제'). 글루코사이드/올리베이트계라 저자극·액정 구조로 보습감이 좋다.
+· 유상 31%에 유화제는 3%뿐 → 유화제:유상 ≈ 0.1로 빠듯. 세틸알코올 1%가 공유화·증점(consistency factor)으로 유화막을 보강하고 크림을 탄탄하게. 세틸알코올은 유화제가 아니라 '보조'인 점이 핵심.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② 알로에겔 22%의 이중 역할 — 이 처방의 핵심</t>
+          <t>② 활성 조합의 의도</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 알로에베라겔은 활성(진정·수분)이면서 '자체 점증'한다 → 별도 점증제(잔탄검) 없이 로션 점도를 만든다. 처방이 단순해지고 사용감 쫀쫀.
-· 세라마이드 리퀴드(수용성)는 수상에 녹는 장벽 보습 활성 → 오일막(동백·녹차씨)과 '유분막 + 장벽' 이중 보습.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>· 석류추출물 + 코엔자임Q10: 항산화·탄력 각도. Q10은 나이 들며 감소하는 세포 에너지 보조 → '탄력·노화 결' 컨셉.
+· 히알루론산 3%: 수분 저장. 유분 31%로 무거울 수 있는 처방에 수분-유분 균형.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>③ 핵심 비율 결정</t>
@@ -1380,12 +1507,12 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 동백(올레인산, 유연)·녹차씨(카테킨) = 가볍고 흡수 좋은 오일 → 로션의 산뜻함.
-· 글리세린 4% = 습윤 적정선(8% 넘기면 끈적·역삼투 주의).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="45" customHeight="1">
+          <t>· 수상 53% + 유상 31% → 유분비 높은 전형적 '영양 크림'(로션이면 유상 10~15%). 건성·노화 타깃.
+· 유화 3%는 최소선 → 세틸알코올 없으면 분리 위험. '유화제 빠듯할 땐 지방알코올로 보완'의 교과서.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>④ 바꾸면?(what-if)</t>
@@ -1393,12 +1520,13 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 알로에겔 → 정제수로 바꾸면 점도 사라짐 → 잔탄검 0.2~0.3%를 글리세린에 선분산해 보충(알로에겔이 숨은 점증제).
-· 유상 20~25% + 유화 3~4%로 키우면 크림으로 전환.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
+          <t>· 로즈힙·햄프는 고불포화(PUFA) 오일 → 산패 빠름. 그런데 보존제는 항균(천연한방)뿐, 산화방지제가 없다 → 비타민E(토코페롤) 0.2~0.5% 추가하면 보존기간 급증. (이 레시피 최대 개선점)
+· 지성·여드름 타깃이면 로즈힙·햄프 대신 스쿠알란·MCT(가볍고 산패 안정), 유상 15~20%로 → 가벼운 크림.
+· 유화제를 몬타노브68로 바꾸면 더 매끈한 액정 질감(히어로 방향).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>⑤ 배우는 점</t>
@@ -1406,8 +1534,8 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· 겔(알로에·로즈플라워겔)은 활성 + 점증을 겸한다 → 처방 간소화.
-· 로션=가벼운 유분+낮은 유화, 크림=높은 유분+높은 유화. 원료가 아니라 비율이 제형을 정한다.</t>
+          <t>· 유화제:유상 비가 낮으면 지방알코올(세틸/세테아릴)로 바디·안정 보강.
+· PUFA 오일엔 반드시 항산화(Vit E) — 항균 보존제와 산화방지제는 다른 일.</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1564,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[밤]  로즈마리근육통연고 — 역설계 심화</t>
+          <t>[로션]  페이셜&amp;바디 라벤더 로션 — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -1455,11 +1583,11 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>산패에 강한 호호바오일 베이스에 왁스로 굳기를 잡고, 근육 이완 EO를 넣은 기능성 무수 밤(롤·연고).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>라벤더워터 + 알로에겔로 산뜻한 수상을 깔고, 가벼운 오일 소량으로 얇은 보습막을 입힌 데일리 로션.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>골격(%)</t>
@@ -1467,46 +1595,45 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>유상 85(호호바 84 + 라벤더오일 &lt;1) · 경화 13(비즈왁스) · 향 3(로즈마리 1 + 마조람 1 + 스피아민트 1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
+          <t>수상 52(라벤더워터) · 활성 28(알로에베라겔 22 + 세라마이드 4 + 캐모마일 2) · 유상 12(동백 8 + 녹차씨 4) · 보습 4(글리세린) · 유화 2(올리브유화왁스) · 방부 1 · 향 &lt;1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① '유화가 없다' — 무수 제형의 설계</t>
+          <t>① 유화 설계 — 왜 유화 2%뿐인데 되나</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· 물이 없으니 유화제·방부제가 아예 불필요. 대신 물 유입 금지(들어가면 그 지점부터 상함)와 산패 관리가 전부.
-· 호호바오일은 '액상 왁스'라 산화에 매우 안정 → 무수 밤 베이스로 이상적(보존기간 길다). 베이스 선택이 곧 보존 전략.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1">
+          <t>· 유상이 12%로 낮아 유화제도 2%면 충분(유화제:유상 ≈ 0.17 → 가벼운 로션 구간). 크림과 비교하면 유분·유화제 모두 절반 이하 → 같은 유화제라도 비율로 로션↔크림이 갈린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② 왁스 비율 = 굳기 (이 레시피의 백미)</t>
+          <t>② 알로에겔 22%의 이중 역할 — 이 처방의 핵심</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 비즈왁스 13% → 적당히 단단한 밤/롤. 특징에 '여름철이라 경화제 양이 많아요' → 계절·사용온도에 따라 왁스%를 조정하는 실전 감각.
-   - 겨울·소프트밤: 비즈왁스 8~10%   - 여름·스틱: 18~25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1">
+          <t>· 알로에베라겔은 활성(진정·수분)이면서 '자체 점증'한다 → 별도 점증제(잔탄검) 없이 로션 점도를 만든다. 처방이 단순해지고 사용감 쫀쫀.
+· 세라마이드 리퀴드(수용성)는 수상에 녹는 장벽 보습 활성 → 오일막(동백·녹차씨)과 '유분막 + 장벽' 이중 보습.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>③ EO 조합의 의도(시너지)</t>
+          <t>③ 핵심 비율 결정</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 로즈마리(혈액순환) + 마조람(근이완·진정) + 스피아민트(쿨링) → '근육통 완화' 테라피. 단일 EO가 아니라 기능을 겹쳐 목적을 만든다.
-· 향(EO) 합 ~3%는 국소 도포라 토너보다 높게. 단, 자극·광독성은 EO 종류별 확인.</t>
+          <t>· 동백(올레인산, 유연)·녹차씨(카테킨) = 가볍고 흡수 좋은 오일 → 로션의 산뜻함.
+· 글리세린 4% = 습윤 적정선(8% 넘기면 끈적·역삼투 주의).</t>
         </is>
       </c>
     </row>
@@ -1518,8 +1645,8 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 베이스를 PUFA 오일(로즈힙 등)로 바꾸면 산패 빨라짐 → 비타민E 필수.
-· 칸데릴라왁스로 바꾸면 식물성이고 비즈왁스보다 단단 → 같은 %라도 더 딱딱(→ %를 약간 낮춘다).</t>
+          <t>· 알로에겔 → 정제수로 바꾸면 점도 사라짐 → 잔탄검 0.2~0.3%를 글리세린에 선분산해 보충(알로에겔이 숨은 점증제).
+· 유상 20~25% + 유화 3~4%로 키우면 크림으로 전환.</t>
         </is>
       </c>
     </row>
@@ -1531,9 +1658,8 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· 무수 = 방부 걱정 없음, 대신 산패·물유입.
-· 왁스%는 온도 민감 → 같은 레시피도 계절에 맞춰 조정.
-· EO는 '겹쳐서' 목적을 만든다(단일보다 블렌딩).</t>
+          <t>· 겔(알로에·로즈플라워겔)은 활성 + 점증을 겸한다 → 처방 간소화.
+· 로션=가벼운 유분+낮은 유화, 크림=높은 유분+높은 유화. 원료가 아니라 비율이 제형을 정한다.</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1688,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[세럼]  콜라겐탄력세럼 — 역설계 심화</t>
+          <t>[밤]  로즈마리근육통연고 — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1699,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>한 줄 요약</t>
@@ -1581,7 +1707,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>알로에겔로 점도를 잡은 수상 세럼에 콜라겐·Q10·비타민E를 몰아넣은 고함량 탄력 세럼.</t>
+          <t>산패에 강한 호호바오일 베이스에 왁스로 굳기를 잡고, 근육 이완 EO를 넣은 기능성 무수 밤(롤·연고).</t>
         </is>
       </c>
     </row>
@@ -1593,46 +1719,46 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>활성 55(알로에겔 45 + Q10 6 + 마린콜라겐 5) · 수상 34(로즈워터) · 보습 3(히알루론) · 방부 7(토코페롤 5 + 한방 2) · 향 &lt;1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>유상 85(호호바 84 + 라벤더오일 &lt;1) · 경화 13(비즈왁스) · 향 3(로즈마리 1 + 마조람 1 + 스피아민트 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① 유화 없는 수상 세럼 — 점도는 알로에겔로</t>
+          <t>① '유화가 없다' — 무수 제형의 설계</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· 세럼은 흡수를 위해 가볍고 유화 없는 수상 제형이 많다. 유화제 없음. 알로에겔 45%가 베이스 + 자체 점증으로 세럼 점도를 만든다(로션과 같은 트릭, 비율만 큼).
-· 활성 합 55% → '앰플·세럼급 기능성 집중'의 전형.</t>
+          <t>· 물이 없으니 유화제·방부제가 아예 불필요. 대신 물 유입 금지(들어가면 그 지점부터 상함)와 산패 관리가 전부.
+· 호호바오일은 '액상 왁스'라 산화에 매우 안정 → 무수 밤 베이스로 이상적(보존기간 길다). 베이스 선택이 곧 보존 전략.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② 지용성 활성을 수상에 넣은 한계 (가장 교훈적)</t>
+          <t>② 왁스 비율 = 굳기 (이 레시피의 백미)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 코엔자임Q10·토코페롤(비타민E)은 본래 지용성. 그런데 유화제/가용화제가 없다 → 수상에 완전히 녹지 못하고 뜨거나 뭉칠 수 있다(분리·이물감 가능).
-· 레시피는 '수용성' Q10 원료와 소량 토코페롤·알로에겔 점도에 기대지만, 안정성은 취약.</t>
+          <t>· 비즈왁스 13% → 적당히 단단한 밤/롤. 특징에 '여름철이라 경화제 양이 많아요' → 계절·사용온도에 따라 왁스%를 조정하는 실전 감각.
+   - 겨울·소프트밤: 비즈왁스 8~10%   - 여름·스틱: 18~25%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>③ 핵심 비율 결정</t>
+          <t>③ EO 조합의 의도(시너지)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 토코페롤 5%는 '방부'로 분류됐지만 실제 역할은 산화방지(지용성 활성 보호) → 역할 태그가 성분의 모든 일을 설명하진 않는다.
-· 히알루론 3%로 수분 저장, 로즈워터로 진정 베이스.</t>
+          <t>· 로즈마리(혈액순환) + 마조람(근이완·진정) + 스피아민트(쿨링) → '근육통 완화' 테라피. 단일 EO가 아니라 기능을 겹쳐 목적을 만든다.
+· 향(EO) 합 ~3%는 국소 도포라 토너보다 높게. 단, 자극·광독성은 EO 종류별 확인.</t>
         </is>
       </c>
     </row>
@@ -1644,8 +1770,8 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 올리브리퀴드(가용화제) 1~2% 추가 → Q10·비타민E가 수상에 투명 분산되어 분리 해결. (1순위 개선)
-· 더 가벼운 세럼: 알로에겔 줄이고 잔탄검 0.3% + 로즈워터로 대체.</t>
+          <t>· 베이스를 PUFA 오일(로즈힙 등)로 바꾸면 산패 빨라짐 → 비타민E 필수.
+· 칸데릴라왁스로 바꾸면 식물성이고 비즈왁스보다 단단 → 같은 %라도 더 딱딱(→ %를 약간 낮춘다).</t>
         </is>
       </c>
     </row>
@@ -1657,8 +1783,9 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· 지용성 활성(Q10·VitE·레티놀)을 수상 제형에 넣으려면 가용화제 필요. 안 그러면 뜬다.
-· 역할 태그 ≠ 전부(토코페롤=산화방지인데 '방부'로 잡힘). 성분의 실제 기능을 보라.</t>
+          <t>· 무수 = 방부 걱정 없음, 대신 산패·물유입.
+· 왁스%는 온도 민감 → 같은 레시피도 계절에 맞춰 조정.
+· EO는 '겹쳐서' 목적을 만든다(단일보다 블렌딩).</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1814,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[세정]  로즈콜라겐 폼클렌징 — 역설계 심화</t>
+          <t>[세럼]  콜라겐탄력세럼 — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1833,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>양쪽성+음이온 계면활성제를 짝지어 순하면서 거품 나는 물비누형 폼클렌저.</t>
+          <t>알로에겔로 점도를 잡은 수상 세럼에 콜라겐·Q10·비타민E를 몰아넣은 고함량 탄력 세럼.</t>
         </is>
       </c>
     </row>
@@ -1718,37 +1845,37 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>수상 55(로즈워터) · 계면 26(코카미도프로필베타인 18 + LES 7) · 보습 11(글리세린) · 활성 7(토마토 4 + 마린콜라겐 4) · 향 &lt;1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="75" customHeight="1">
+          <t>활성 55(알로에겔 45 + Q10 6 + 마린콜라겐 5) · 수상 34(로즈워터) · 보습 3(히알루론) · 방부 7(토코페롤 5 + 한방 2) · 향 &lt;1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① 계면활성제 페어링 — 왜 두 종류인가 (핵심)</t>
+          <t>① 유화 없는 수상 세럼 — 점도는 알로에겔로</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· LES(음이온) = 주 세정·거품력. 단독이면 세정력 강하나 자극·건조.
-· 코카미도프로필베타인(양쪽성) = 보조 거품 + 음이온의 자극 완화, 거품 크리미. → '음이온+양쪽성'은 순하면서 거품 유지의 정석.
-· 베타인(18%)을 음이온(7%)보다 많이 써 순함 쪽에 무게 → 로즈워터 베이스와 함께 민감·건성도 겨냥.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>· 세럼은 흡수를 위해 가볍고 유화 없는 수상 제형이 많다. 유화제 없음. 알로에겔 45%가 베이스 + 자체 점증으로 세럼 점도를 만든다(로션과 같은 트릭, 비율만 큼).
+· 활성 합 55% → '앰플·세럼급 기능성 집중'의 전형.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="45" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② 글리세린 11%의 의도</t>
+          <t>② 지용성 활성을 수상에 넣은 한계 (가장 교훈적)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 세정은 본질적으로 씻어내며 건조. 글리세린을 높게(11%) 넣어 세정 후 당김 보완(스킨케어 로션의 4%보다 훨씬 높은 이유 = 세정 제형이라서).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
+          <t>· 코엔자임Q10·토코페롤(비타민E)은 본래 지용성. 그런데 유화제/가용화제가 없다 → 수상에 완전히 녹지 못하고 뜨거나 뭉칠 수 있다(분리·이물감 가능).
+· 레시피는 '수용성' Q10 원료와 소량 토코페롤·알로에겔 점도에 기대지만, 안정성은 취약.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>③ 핵심 비율 결정</t>
@@ -1756,8 +1883,8 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 계면 총 26% → 일반 폼/젤 클렌저 구간(5~10% 순한 워시, 20~40% 진한 폼).
-· 활성(토마토·콜라겐)은 씻겨나가는 제형이라 효능 기대 제한적 — '컨셉·마케팅 포인트'에 가깝다.</t>
+          <t>· 토코페롤 5%는 '방부'로 분류됐지만 실제 역할은 산화방지(지용성 활성 보호) → 역할 태그가 성분의 모든 일을 설명하진 않는다.
+· 히알루론 3%로 수분 저장, 로즈워터로 진정 베이스.</t>
         </is>
       </c>
     </row>
@@ -1769,13 +1896,12 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 지성·여드름용: LES(음이온)↑ 또는 추가로 세정력 강화, 글리세린 낮춤.
-· 더 순하게(민감): 음이온 빼고 데실글루코사이드(비이온) + 베타인 조합.
-· pH: 음이온(LES)이 알칼리로 기울기 쉬움 → 구연산으로 약산성(5~6) 보정 권장.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>· 올리브리퀴드(가용화제) 1~2% 추가 → Q10·비타민E가 수상에 투명 분산되어 분리 해결. (1순위 개선)
+· 더 가벼운 세럼: 알로에겔 줄이고 잔탄검 0.3% + 로즈워터로 대체.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>⑤ 배우는 점</t>
@@ -1783,9 +1909,8 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· 계면활성제는 '짝지어' 쓴다: 음이온(세정)+양쪽성(순함)+비이온(저자극). 비율로 세정력↔순함 조절.
-· 세정엔 글리세린 넉넉히(당김 보완).
-· 워시오프 제형의 활성은 효능보다 컨셉 — 돈을 어디 쓸지 판단하는 눈.</t>
+          <t>· 지용성 활성(Q10·VitE·레티놀)을 수상 제형에 넣으려면 가용화제 필요. 안 그러면 뜬다.
+· 역할 태그 ≠ 전부(토코페롤=산화방지인데 '방부'로 잡힘). 성분의 실제 기능을 보라.</t>
         </is>
       </c>
     </row>
@@ -1814,7 +1939,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[토너·미스트]  촉촉 아르간 미스트 — 역설계 심화</t>
+          <t>[세정]  로즈콜라겐 폼클렌징 — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1950,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="28" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>한 줄 요약</t>
@@ -1833,11 +1958,11 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>로즈워터 미스트에 '리포좀화한 아르간오일'을 넣어, 가용화제 없이 오일 보습을 수상에 담은 미스트.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+          <t>양쪽성+음이온 계면활성제를 짝지어 순하면서 거품 나는 물비누형 폼클렌저.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>골격(%)</t>
@@ -1845,43 +1970,46 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>수상 99(로즈워터 94 + 워터아르간 5) · 방부 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>수상 55(로즈워터) · 계면 26(코카미도프로필베타인 18 + LES 7) · 보습 11(글리세린) · 활성 7(토마토 4 + 마린콜라겐 4) · 향 &lt;1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="75" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① 가용화 문제의 영리한 우회</t>
+          <t>① 계면활성제 페어링 — 왜 두 종류인가 (핵심)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· 보통 미스트에 오일을 넣으면 분리 → 가용화제(올리브리퀴드) 필요. 여기선 '워터아르간'(아르간오일을 레시틴으로 감싼 리포좀) 사용 → 이미 수용화돼 물에 그냥 섞으면 분산. 가용화제·EO 분리 걱정 없이 오일 보습을 미스트에.</t>
+          <t>· LES(음이온) = 주 세정·거품력. 단독이면 세정력 강하나 자극·건조.
+· 코카미도프로필베타인(양쪽성) = 보조 거품 + 음이온의 자극 완화, 거품 크리미. → '음이온+양쪽성'은 순하면서 거품 유지의 정석.
+· 베타인(18%)을 음이온(7%)보다 많이 써 순함 쪽에 무게 → 로즈워터 베이스와 함께 민감·건성도 겨냥.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② 왜 거의 다 물인가</t>
+          <t>② 글리세린 11%의 의도</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 미스트는 분사·빠른 흡수가 목적 → 수상 99%, 점증·유화 없음. 오일 보습은 리포좀 5%로만 얹음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>· 세정은 본질적으로 씻어내며 건조. 글리세린을 높게(11%) 넣어 세정 후 당김 보완(스킨케어 로션의 4%보다 훨씬 높은 이유 = 세정 제형이라서).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>③ 핵심 비율</t>
+          <t>③ 핵심 비율 결정</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 방부 1% 필수(물 99%는 미생물 천국). 로즈워터가 정제수 대신 → 진정 베이스 + 은은한 향.</t>
+          <t>· 계면 총 26% → 일반 폼/젤 클렌저 구간(5~10% 순한 워시, 20~40% 진한 폼).
+· 활성(토마토·콜라겐)은 씻겨나가는 제형이라 효능 기대 제한적 — '컨셉·마케팅 포인트'에 가깝다.</t>
         </is>
       </c>
     </row>
@@ -1893,13 +2021,13 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 일반 아르간오일을 넣고 싶으면 올리브리퀴드 1~2%로 가용화(투명 미스트).
-· EO를 넣으려면 역시 가용화제 필수(안 그러면 유막·자극).
-· 피부타입별 워터로 교체(편백=지성, 캐모마일=민감).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+          <t>· 지성·여드름용: LES(음이온)↑ 또는 추가로 세정력 강화, 글리세린 낮춤.
+· 더 순하게(민감): 음이온 빼고 데실글루코사이드(비이온) + 베타인 조합.
+· pH: 음이온(LES)이 알칼리로 기울기 쉬움 → 구연산으로 약산성(5~6) 보정 권장.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>⑤ 배우는 점</t>
@@ -1907,8 +2035,9 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· '리포좀/워터형 오일'은 수상 제형에 오일을 넣는 또 하나의 길(가용화제 대안).
-· 물 많은 제형 = 방부가 생명.</t>
+          <t>· 계면활성제는 '짝지어' 쓴다: 음이온(세정)+양쪽성(순함)+비이온(저자극). 비율로 세정력↔순함 조절.
+· 세정엔 글리세린 넉넉히(당김 보완).
+· 워시오프 제형의 활성은 효능보다 컨셉 — 돈을 어디 쓸지 판단하는 눈.</t>
         </is>
       </c>
     </row>
@@ -1937,7 +2066,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[젤]  안티 셀룰라이트 젤 — 역설계 심화</t>
+          <t>[토너·미스트]  촉촉 아르간 미스트 — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -1948,7 +2077,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>한 줄 요약</t>
@@ -1956,11 +2085,11 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>로즈워터에 점증제(하이셀)로 가벼운 젤 바디를 주고 순환·수렴 EO를 얹은 바디 젤.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>로즈워터 미스트에 '리포좀화한 아르간오일'을 넣어, 가용화제 없이 오일 보습을 수상에 담은 미스트.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>골격(%)</t>
@@ -1968,31 +2097,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>수상 92(로즈워터) · 보습 5(글리세린) · 점증/pH 1(하이셀) · 향 2(그레이프프룻·주니퍼·제라늄) · 유상 &lt;1(페퍼민트)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>수상 99(로즈워터 94 + 워터아르간 5) · 방부 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① 점증제로 '젤'을 만든다</t>
+          <t>① 가용화 문제의 영리한 우회</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· 하이셀(HEC, 하이드록시에틸셀룰로오스) 1% 이하로 로즈워터에 점도를 줘 흐르지 않는 젤. 유화·오일 거의 없는 '수상 젤' 전형. 하이셀은 수화에 시간·교반 필요(덩어리 주의).</t>
+          <t>· 보통 미스트에 오일을 넣으면 분리 → 가용화제(올리브리퀴드) 필요. 여기선 '워터아르간'(아르간오일을 레시틴으로 감싼 리포좀) 사용 → 이미 수용화돼 물에 그냥 섞으면 분산. 가용화제·EO 분리 걱정 없이 오일 보습을 미스트에.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② EO 블렌드의 의도</t>
+          <t>② 왜 거의 다 물인가</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 그레이프프룻·주니퍼베리·싸이프러스·제라늄 = 림프·순환·수렴 각도의 '다이어트/셀룰라이트' 컨셉. 향(EO) 합 ~2%.</t>
+          <t>· 미스트는 분사·빠른 흡수가 목적 → 수상 99%, 점증·유화 없음. 오일 보습은 리포좀 5%로만 얹음.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2133,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 글리세린 5%로 촉촉·젤 유연성. EO가 가용화제 없이 들어가 소량이라 버티지만, 많으면 분리·자극.</t>
+          <t>· 방부 1% 필수(물 99%는 미생물 천국). 로즈워터가 정제수 대신 → 진정 베이스 + 은은한 향.</t>
         </is>
       </c>
     </row>
@@ -2016,9 +2145,9 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 더 맑고 탄탄한 젤 → 카보머 0.3% + 중화(TEA).
-· EO를 늘리려면 올리브리퀴드로 가용화.
-· 이 레시피엔 방부가 안 보인다 → 물 92%엔 방부 반드시 추가(중요 보완).</t>
+          <t>· 일반 아르간오일을 넣고 싶으면 올리브리퀴드 1~2%로 가용화(투명 미스트).
+· EO를 넣으려면 역시 가용화제 필수(안 그러면 유막·자극).
+· 피부타입별 워터로 교체(편백=지성, 캐모마일=민감).</t>
         </is>
       </c>
     </row>
@@ -2030,8 +2159,8 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· 젤 = 수상 + 점증제. 점증제 종류(잔탄/HEC/카보머)로 질감·투명도가 갈림.
-· EO는 소량이라도 가용화가 정석.</t>
+          <t>· '리포좀/워터형 오일'은 수상 제형에 오일을 넣는 또 하나의 길(가용화제 대안).
+· 물 많은 제형 = 방부가 생명.</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2189,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[팩·마스크·패드]  안티 셀룰라이트 바디팩 — 역설계 심화</t>
+          <t>[젤]  안티 셀룰라이트 젤 — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -2079,11 +2208,11 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>그린클레이로 흡착·디톡스하는 바디팩. 물로 개어 EO를 더한 워시오프 클레이팩.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
+          <t>로즈워터에 점증제(하이셀)로 가벼운 젤 바디를 주고 순환·수렴 EO를 얹은 바디 젤.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>골격(%)</t>
@@ -2091,31 +2220,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>클레이 54(그린클레이) · 수상 43(정제수) · 향 2(그레이프프룻·제라늄·싸이프러스)</t>
+          <t>수상 92(로즈워터) · 보습 5(글리세린) · 점증/pH 1(하이셀) · 향 2(그레이프프룻·주니퍼·제라늄) · 유상 &lt;1(페퍼민트)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① 클레이가 주인공</t>
+          <t>① 점증제로 '젤'을 만든다</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· 그린클레이(일라이트·몽모릴로나이트계)가 피지·노폐물을 흡착. 물 43%로 개어 바르는 농도. 금속 도구 피하고(클레이 활성 저하), 굳기 전 씻어낸다(과건조=당김).</t>
+          <t>· 하이셀(HEC, 하이드록시에틸셀룰로오스) 1% 이하로 로즈워터에 점도를 줘 흐르지 않는 젤. 유화·오일 거의 없는 '수상 젤' 전형. 하이셀은 수화에 시간·교반 필요(덩어리 주의).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② 왜 방부·유화가 없나</t>
+          <t>② EO 블렌드의 의도</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 클레이+물이지만 '쓸 때 개서' 또는 단기 사용 전제 → 완제 보존은 취약. 즉석 또는 소량·냉장(장기 보관 시 방부 필요).</t>
+          <t>· 그레이프프룻·주니퍼베리·싸이프러스·제라늄 = 림프·순환·수렴 각도의 '다이어트/셀룰라이트' 컨셉. 향(EO) 합 ~2%.</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2256,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 클레이:물 ≈ 1:0.8 → 바르기 좋은 반죽. 물이 많으면 흐르고 적으면 금방 굳음. EO 2%는 바디·워시오프라 비교적 높게.</t>
+          <t>· 글리세린 5%로 촉촉·젤 유연성. EO가 가용화제 없이 들어가 소량이라 버티지만, 많으면 분리·자극.</t>
         </is>
       </c>
     </row>
@@ -2139,9 +2268,9 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 얼굴용은 클레이 농도 낮추고 보습(글리세린·꿀) 추가해 과건조 완화.
-· 보습 클레이=카올린(순함), 피지흡착↑=벤토나이트.
-· 하이드로졸로 개면 진정 더.</t>
+          <t>· 더 맑고 탄탄한 젤 → 카보머 0.3% + 중화(TEA).
+· EO를 늘리려면 올리브리퀴드로 가용화.
+· 이 레시피엔 방부가 안 보인다 → 물 92%엔 방부 반드시 추가(중요 보완).</t>
         </is>
       </c>
     </row>
@@ -2153,8 +2282,8 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· 클레이팩은 '흡착 + 수분증발'이 원리 → 굳기 전 세척·과건조 주의.
-· 물로 개는 제형은 즉석/단기.</t>
+          <t>· 젤 = 수상 + 점증제. 점증제 종류(잔탄/HEC/카보머)로 질감·투명도가 갈림.
+· EO는 소량이라도 가용화가 정석.</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2312,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[페이스·바디오일]  아르간페이셜오일 — 역설계 심화</t>
+          <t>[팩·마스크·패드]  안티 셀룰라이트 바디팩 — 역설계 심화</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2331,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>아르간+로즈힙 2종 블렌드의 무수 페이셜오일. 오일을 '지방산 프로파일'로 고른 사례.</t>
+          <t>그린클레이로 흡착·디톡스하는 바디팩. 물로 개어 EO를 더한 워시오프 클레이팩.</t>
         </is>
       </c>
     </row>
@@ -2214,31 +2343,31 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>유상 100(아르간 60 + 로즈힙 40) · 향 &lt;1(네롤리 EO)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="45" customHeight="1">
+          <t>클레이 54(그린클레이) · 수상 43(정제수) · 향 2(그레이프프룻·제라늄·싸이프러스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>① 왜 이 2종 오일</t>
+          <t>① 클레이가 주인공</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>· 아르간(올레인·리놀레산 균형, 토코페롤·폴리페놀 풍부 → 비교적 안정)과 로즈힙(고 리놀레/리놀렌산=PUFA, 재생·노화 각도지만 산패 빠름)의 조합. 아르간의 토코페롤이 로즈힙 산패를 일부 늦춘다 → '안정 오일 + 기능 오일' 페어링.</t>
+          <t>· 그린클레이(일라이트·몽모릴로나이트계)가 피지·노폐물을 흡착. 물 43%로 개어 바르는 농도. 금속 도구 피하고(클레이 활성 저하), 굳기 전 씻어낸다(과건조=당김).</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>② 무수 설계</t>
+          <t>② 왜 방부·유화가 없나</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>· 물 없음 → 방부 불필요, 물 유입 금지. 산패가 유일한 적 → 차광·밀폐, 토코페롤 추가 여지.</t>
+          <t>· 클레이+물이지만 '쓸 때 개서' 또는 단기 사용 전제 → 완제 보존은 취약. 즉석 또는 소량·냉장(장기 보관 시 방부 필요).</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2379,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>· 60:40은 '기능(로즈힙)을 충분히 주되 아르간으로 안정·발림 확보'. EO는 2방울(&lt;1%)로 향만.</t>
+          <t>· 클레이:물 ≈ 1:0.8 → 바르기 좋은 반죽. 물이 많으면 흐르고 적으면 금방 굳음. EO 2%는 바디·워시오프라 비교적 높게.</t>
         </is>
       </c>
     </row>
@@ -2262,13 +2391,13 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>· 지성·여드름이면 로즈힙 줄이고 스쿠알란·호호바(말라세지아 세이프·가벼움)로.
-· 미스트 위 덧바르는 3초 보습용엔 이대로 좋음.
-· 토코페롤 0.3% 추가로 보존 강화.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="45" customHeight="1">
+          <t>· 얼굴용은 클레이 농도 낮추고 보습(글리세린·꿀) 추가해 과건조 완화.
+· 보습 클레이=카올린(순함), 피지흡착↑=벤토나이트.
+· 하이드로졸로 개면 진정 더.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>⑤ 배우는 점</t>
@@ -2276,8 +2405,8 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>· 오일은 '지방산 프로파일'로 고른다(올레인=안정·유연, 리놀레=가벼움·장벽, PUFA=기능이나 산패↑).
-· 블렌딩으로 안정×기능 균형. EO는 반드시 캐리어에 희석.</t>
+          <t>· 클레이팩은 '흡착 + 수분증발'이 원리 → 굳기 전 세척·과건조 주의.
+· 물로 개는 제형은 즉석/단기.</t>
         </is>
       </c>
     </row>
